--- a/data/trans_orig/IP07C01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C01-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25776</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40335</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>46180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89810</t>
+          <t>89788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111654</t>
+          <t>111658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106031</t>
+          <t>106828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129376</t>
+          <t>129608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202934</t>
+          <t>203647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>233036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70326</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91333</t>
+          <t>90980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77771</t>
+          <t>77439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100328</t>
+          <t>100192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152979</t>
+          <t>154351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185248</t>
+          <t>185007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45570</t>
+          <t>45786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61959</t>
+          <t>61741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28090</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141559</t>
+          <t>141139</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168342</t>
+          <t>168791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151488</t>
+          <t>149338</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179533</t>
+          <t>178687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>299468</t>
+          <t>299389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>337717</t>
+          <t>337005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105827</t>
+          <t>105877</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133162</t>
+          <t>132311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117059</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145176</t>
+          <t>145744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231239</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>269357</t>
+          <t>270952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24406</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45422</t>
+          <t>45930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35017</t>
+          <t>35217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>29001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>42986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61497</t>
+          <t>60405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59680</t>
+          <t>58552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81726</t>
+          <t>81663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90458</t>
+          <t>90908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115567</t>
+          <t>114770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156059</t>
+          <t>155131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189106</t>
+          <t>188332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103220</t>
+          <t>103895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125629</t>
+          <t>126776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94576</t>
+          <t>94689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119632</t>
+          <t>119452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205991</t>
+          <t>206742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238716</t>
+          <t>239372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31927</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>31108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58851</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46987</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65453</t>
+          <t>64848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132059</t>
+          <t>130598</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161455</t>
+          <t>160436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241060</t>
+          <t>238525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282589</t>
+          <t>282153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158798</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187618</t>
+          <t>185398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142485</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>171804</t>
+          <t>172721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308749</t>
+          <t>309644</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>351898</t>
+          <t>352533</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>23325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122941</t>
+          <t>123244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148788</t>
+          <t>148845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111939</t>
+          <t>112627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137146</t>
+          <t>138666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242419</t>
+          <t>243455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279623</t>
+          <t>280622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,33%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83146</t>
+          <t>82262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80988</t>
+          <t>81689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105820</t>
+          <t>106983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168785</t>
+          <t>169796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205522</t>
+          <t>206754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41719</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70401</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90168</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,16%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>36990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>19557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>33487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46762</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>66002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>167309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200458</t>
+          <t>199040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172603</t>
+          <t>173689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205633</t>
+          <t>204028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>351422</t>
+          <t>354215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396568</t>
+          <t>396015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124635</t>
+          <t>124693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154979</t>
+          <t>155355</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>120053</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150206</t>
+          <t>150078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252660</t>
+          <t>252944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296672</t>
+          <t>293922</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>27389</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49743</t>
+          <t>48056</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85727</t>
+          <t>84799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127491</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96939</t>
+          <t>98371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130271</t>
+          <t>131753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187508</t>
+          <t>190700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250690</t>
+          <t>249536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62135</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62114</t>
+          <t>61635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94453</t>
+          <t>93618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96551</t>
+          <t>95006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150121</t>
+          <t>148141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>23327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>34977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>108750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158813</t>
+          <t>157478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>168026</t>
+          <t>167731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248842</t>
+          <t>248949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311926</t>
+          <t>316372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>85644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>84114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118807</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>141756</t>
+          <t>136815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>196475</t>
+          <t>196646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>34203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
